--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY424"/>
+  <dimension ref="A1:AZ424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628662</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628464</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628651</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628915</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628957</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628940</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628901</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628976</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1623,6 +1668,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628795</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1728,6 +1778,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628824</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1834,6 +1889,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498404</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1942,6 +2002,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629085</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2041,6 +2106,11 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498400</t>
         </is>
       </c>
     </row>
@@ -2144,6 +2214,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628446</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2243,6 +2318,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498409</t>
         </is>
       </c>
     </row>
@@ -2346,6 +2426,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628404</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2446,6 +2531,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73626347</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2547,6 +2637,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498397</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2655,6 +2750,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629094</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2771,6 +2871,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165782</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2887,6 +2992,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165784</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3003,6 +3113,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165786</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3109,6 +3224,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498405</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3209,6 +3329,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628903</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3317,6 +3442,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628816</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3417,6 +3547,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628826</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3518,6 +3653,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498407</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3626,6 +3766,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73626355</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3730,6 +3875,11 @@
       <c r="AY30" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498406</t>
         </is>
       </c>
     </row>
@@ -3839,6 +3989,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628904</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3945,6 +4100,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498395</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4049,6 +4209,11 @@
       <c r="AY33" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498408</t>
         </is>
       </c>
     </row>
@@ -4158,6 +4323,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73626350</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4262,6 +4432,11 @@
       <c r="AY35" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498402</t>
         </is>
       </c>
     </row>
@@ -4371,6 +4546,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628798</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4478,6 +4658,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628898</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4590,6 +4775,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629127</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4696,6 +4886,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498410</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4800,6 +4995,11 @@
       <c r="AY40" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498401</t>
         </is>
       </c>
     </row>
@@ -4903,6 +5103,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629162</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5004,6 +5209,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629227</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5105,6 +5315,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629244</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5206,6 +5421,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629392</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5306,6 +5526,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629192</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5407,6 +5632,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165787</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5523,6 +5753,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165781</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5639,6 +5874,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165783</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5755,6 +5995,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165785</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5855,6 +6100,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629205</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5968,6 +6218,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629175</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6076,6 +6331,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629390</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6186,6 +6446,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629320</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6298,6 +6563,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73625399</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6410,6 +6680,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73625532</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6517,6 +6792,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629332</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6617,6 +6897,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73628984</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6730,6 +7015,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629051</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6840,6 +7130,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100519516</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6950,6 +7245,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100527070</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7070,6 +7370,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100519297</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7186,6 +7491,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165771</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7300,6 +7610,11 @@
       <c r="AY63" t="inlineStr">
         <is>
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165772</t>
         </is>
       </c>
     </row>
@@ -7403,6 +7718,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73632568</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7504,6 +7824,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73632584</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7620,6 +7945,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165780</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7728,6 +8058,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639653</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7828,6 +8163,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73632649</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7936,6 +8276,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98642268</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8044,6 +8389,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98642316</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8151,6 +8501,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73632628</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8258,6 +8613,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73632616</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8371,6 +8731,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73630349</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8487,6 +8852,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165770</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8603,6 +8973,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165773</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8716,6 +9091,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73630011</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8829,6 +9209,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73630321</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8930,6 +9315,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498340</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9031,6 +9421,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498319</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9132,6 +9527,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498341</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9237,6 +9637,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73630889</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9343,6 +9748,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498328</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9444,6 +9854,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498321</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9545,6 +9960,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165803</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9646,6 +10066,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165804</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9747,6 +10172,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165805</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9847,6 +10277,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73630346</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9960,6 +10395,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629593</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10060,6 +10500,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73630434</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10161,6 +10606,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498343</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10261,6 +10711,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629615</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10369,6 +10824,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73630945</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10485,6 +10945,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165778</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10601,6 +11066,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165779</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10709,6 +11179,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639412</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10817,6 +11292,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98642436</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10934,6 +11414,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98642485</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11040,6 +11525,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498327</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11141,6 +11631,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498339</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11257,6 +11752,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165769</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11365,6 +11865,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73630328</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11473,6 +11978,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73630333</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11574,6 +12084,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498326</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11675,6 +12190,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498342</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11779,6 +12299,11 @@
       <c r="AY105" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498324</t>
         </is>
       </c>
     </row>
@@ -11888,6 +12413,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73630863</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11994,6 +12524,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498323</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12103,6 +12638,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78690212</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12209,6 +12749,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498320</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12336,6 +12881,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295236</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12443,6 +12993,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295235</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12565,6 +13120,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295231</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12687,6 +13247,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295232</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12800,6 +13365,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629669</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12915,6 +13485,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134942090</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13022,6 +13597,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295234</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13127,6 +13707,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256169</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13232,6 +13817,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256193</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13337,6 +13927,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256196</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13437,6 +14032,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256679</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13542,6 +14142,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256690</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13643,6 +14248,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165768</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13748,6 +14358,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256658</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13853,6 +14468,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256570</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13958,6 +14578,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256603</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14063,6 +14688,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256574</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14168,6 +14798,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256607</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14273,6 +14908,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256611</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14378,6 +15018,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73633716</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14479,6 +15124,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73631766</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14591,6 +15241,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639894</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14699,6 +15354,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110905882</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14799,6 +15459,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73631049</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14911,6 +15576,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98640837</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15034,6 +15704,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639927</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15142,6 +15817,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73631547</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15266,6 +15946,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73632160</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15383,6 +16068,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107864294</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15498,6 +16188,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100519912</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15613,6 +16308,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100519988</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15720,6 +16420,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73632055</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15832,6 +16537,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73632052</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15947,6 +16657,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98640916</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16060,6 +16775,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629683</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16161,6 +16881,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629735</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16262,6 +16987,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165806</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16375,6 +17105,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629687</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16483,6 +17218,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73629694</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16600,6 +17340,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98638810</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16708,6 +17453,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98639270</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16824,6 +17574,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/47343832</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16938,6 +17693,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66981238</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17052,6 +17812,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57915539</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17162,6 +17927,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57915575</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17272,6 +18042,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120732921</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17396,6 +18171,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89722719</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17515,6 +18295,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60883524</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17631,6 +18416,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92638773</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17745,6 +18535,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57915665</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17856,6 +18651,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/47352694</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17974,6 +18774,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60878738</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18084,6 +18889,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66981234</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18194,6 +19004,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87492331</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18304,6 +19119,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87492360</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18415,6 +19235,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93679452</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18525,6 +19350,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87492337</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18640,6 +19470,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79175108</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18751,6 +19586,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/47352175</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18858,6 +19698,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713471</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18965,6 +19810,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713466</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19075,6 +19925,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944166</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19186,6 +20041,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713467</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19300,6 +20160,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944032</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19416,6 +20281,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165777</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19524,6 +20394,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110907867</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19640,6 +20515,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944154</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19752,6 +20632,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713465</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19859,6 +20744,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124699853</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19966,6 +20856,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713469</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20066,6 +20961,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66257145</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20170,6 +21070,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256205</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20274,6 +21179,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66257130</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20379,6 +21289,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256252</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20484,6 +21399,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66257091</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20589,6 +21509,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256525</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20694,6 +21619,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256704</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20807,6 +21737,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256512</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20912,6 +21847,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256533</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21017,6 +21957,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256756</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21133,6 +22078,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165775</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21249,6 +22199,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165776</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21353,6 +22308,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256488</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21464,6 +22424,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256542</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21575,6 +22540,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256743</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21680,6 +22650,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256500</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21785,6 +22760,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256724</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21903,6 +22883,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98640036</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22003,6 +22988,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256761</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22113,6 +23103,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100520994</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22218,6 +23213,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256801</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22323,6 +23323,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256794</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22430,6 +23435,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713472</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22537,6 +23547,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713477</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22644,6 +23659,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713473</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22751,6 +23771,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713474</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22858,6 +23883,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713475</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22965,6 +23995,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713476</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23075,6 +24110,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124201237</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23181,6 +24221,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853322</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23282,6 +24327,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497564</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23386,6 +24436,11 @@
       <c r="AY211" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497563</t>
         </is>
       </c>
     </row>
@@ -23495,6 +24550,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853292</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23599,6 +24659,11 @@
       <c r="AY213" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497567</t>
         </is>
       </c>
     </row>
@@ -23707,6 +24772,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853733</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23813,6 +24883,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853789</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23923,6 +24998,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853600</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24030,6 +25110,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853692</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24137,6 +25222,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853766</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24239,6 +25329,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853471</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -24341,6 +25436,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853648</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24442,6 +25542,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853960</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24542,6 +25647,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853832</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24649,6 +25759,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853997</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24751,6 +25866,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853891</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24856,6 +25976,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256962</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24961,6 +26086,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256994</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25068,6 +26198,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100525981</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -25181,6 +26316,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66257001</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -25296,6 +26436,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100521613</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25401,6 +26546,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256973</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25506,6 +26656,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256825</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25606,6 +26761,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256887</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25711,6 +26871,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256810</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25816,6 +26981,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256922</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25921,6 +27091,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256931</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26026,6 +27201,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256907</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -26131,6 +27311,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256865</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -26236,6 +27421,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66256872</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -26350,6 +27540,11 @@
       <c r="AY239" t="inlineStr">
         <is>
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
+        </is>
+      </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165774</t>
         </is>
       </c>
     </row>
@@ -26459,6 +27654,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703607</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26577,6 +27777,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944605</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -26693,6 +27898,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165797</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26809,6 +28019,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165798</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -26909,6 +28124,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73852230</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27010,6 +28230,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165795</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -27111,6 +28336,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165796</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -27221,6 +28451,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73852954</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -27328,6 +28563,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853053</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27435,6 +28675,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73851468</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27542,6 +28787,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73852973</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27644,6 +28894,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73852925</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -27744,6 +28999,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853244</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -27846,6 +29106,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73853238</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -27952,6 +29217,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73854205</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -28058,6 +29328,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73854251</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -28164,6 +29439,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497575</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -28269,6 +29549,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73854108</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28374,6 +29659,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73854381</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -28480,6 +29770,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497576</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -28580,6 +29875,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73854326</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -28681,6 +29981,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497574</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -28781,6 +30086,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73854414</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -28887,6 +30197,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497584</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -28988,6 +30303,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497573</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -29092,6 +30412,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703813</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -29193,6 +30518,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165794</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -29294,6 +30624,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497572</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -29398,6 +30733,11 @@
       <c r="AY268" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497583</t>
         </is>
       </c>
     </row>
@@ -29502,6 +30842,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73854562</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -29601,6 +30946,11 @@
       <c r="AY270" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497581</t>
         </is>
       </c>
     </row>
@@ -29710,6 +31060,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73854341</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -29809,6 +31164,11 @@
       <c r="AY272" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497571</t>
         </is>
       </c>
     </row>
@@ -29912,6 +31272,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703347</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -30018,6 +31383,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703361</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -30123,6 +31493,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703365</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -30228,6 +31603,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703265</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -30333,6 +31713,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703305</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -30438,6 +31823,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703335</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -30543,6 +31933,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703373</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -30648,6 +32043,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703419</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -30761,6 +32161,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703376</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -30874,6 +32279,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703409</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -30987,6 +32397,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703320</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -31099,6 +32514,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703275</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -31204,6 +32624,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73703481</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -31304,6 +32729,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850600</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -31404,6 +32834,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850814</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -31504,6 +32939,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850876</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -31612,6 +33052,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850770</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -31725,6 +33170,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73851050</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -31832,6 +33282,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850907</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -31944,6 +33399,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850565</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -32051,6 +33511,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850974</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -32158,6 +33623,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850922</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -32270,6 +33740,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850944</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -32376,6 +33851,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73851348</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -32482,6 +33962,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497601</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -32587,6 +34072,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73851362</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -32693,6 +34183,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497606</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -32794,6 +34289,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497602</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -32895,6 +34395,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165801</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -32995,6 +34500,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73851264</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -33101,6 +34611,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497608</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -33201,6 +34716,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73851151</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -33313,6 +34833,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73851214</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -33420,6 +34945,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73851313</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -33524,6 +35054,11 @@
       <c r="AY307" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497603</t>
         </is>
       </c>
     </row>
@@ -33633,6 +35168,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73851365</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -33740,6 +35280,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73851408</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -33844,6 +35389,11 @@
       <c r="AY310" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497604</t>
         </is>
       </c>
     </row>
@@ -33958,6 +35508,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73851390</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -34062,6 +35617,11 @@
       <c r="AY312" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107497600</t>
         </is>
       </c>
     </row>
@@ -34165,6 +35725,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73851302</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -34265,6 +35830,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73854720</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -34365,6 +35935,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73854628</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -34467,6 +36042,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702139</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -34573,6 +36153,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702097</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -34679,6 +36264,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702204</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -34785,6 +36375,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702233</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -34891,6 +36486,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702248</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -34997,6 +36597,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702273</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -35103,6 +36708,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412258</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -35208,6 +36818,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702280</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -35312,6 +36927,11 @@
       <c r="AY324" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412260</t>
         </is>
       </c>
     </row>
@@ -35420,6 +37040,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702292</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -35521,6 +37146,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412273</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -35622,6 +37252,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412257</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -35723,6 +37358,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412262</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -35824,6 +37464,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412272</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -35930,6 +37575,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412279</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -36031,6 +37681,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412265</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -36139,6 +37794,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702142</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -36240,6 +37900,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412275</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -36341,6 +38006,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412264</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -36445,6 +38115,11 @@
       <c r="AY335" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412268</t>
         </is>
       </c>
     </row>
@@ -36559,6 +38234,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702275</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -36665,6 +38345,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412266</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -36769,6 +38454,11 @@
       <c r="AY338" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412261</t>
         </is>
       </c>
     </row>
@@ -36878,6 +38568,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702143</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -36984,6 +38679,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412271</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -37083,6 +38783,11 @@
       <c r="AY341" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412276</t>
         </is>
       </c>
     </row>
@@ -37187,6 +38892,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702239</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -37286,6 +38996,11 @@
       <c r="AY343" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412278</t>
         </is>
       </c>
     </row>
@@ -37390,6 +39105,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702149</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -37491,6 +39211,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107412259</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -37596,6 +39321,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702013</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -37696,6 +39426,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702312</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -37797,6 +39532,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165789</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -37897,6 +39637,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702330</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -37996,6 +39741,11 @@
       <c r="AY350" t="inlineStr">
         <is>
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
+        </is>
+      </c>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165793</t>
         </is>
       </c>
     </row>
@@ -38105,6 +39855,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702060</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -38212,6 +39967,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702366</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -38319,6 +40079,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702070</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -38426,6 +40191,11 @@
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702377</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -38528,6 +40298,11 @@
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702384</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -38630,6 +40405,11 @@
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702360</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -38741,6 +40521,11 @@
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410436</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -38852,6 +40637,11 @@
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410956</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -38966,6 +40756,11 @@
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128411799</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -39065,6 +40860,11 @@
       <c r="AY360" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498305</t>
         </is>
       </c>
     </row>
@@ -39182,6 +40982,11 @@
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128411275</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -39296,6 +41101,11 @@
         </is>
       </c>
       <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410210</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -39406,6 +41216,11 @@
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128411314</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -39520,6 +41335,11 @@
         </is>
       </c>
       <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128412502</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -39635,6 +41455,11 @@
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128414164</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -39750,6 +41575,11 @@
         </is>
       </c>
       <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128412160</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -39860,6 +41690,11 @@
         </is>
       </c>
       <c r="AY367" t="inlineStr"/>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128412770</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -39978,6 +41813,11 @@
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128411755</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -40086,6 +41926,11 @@
         </is>
       </c>
       <c r="AY369" t="inlineStr"/>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702512</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -40196,6 +42041,11 @@
         </is>
       </c>
       <c r="AY370" t="inlineStr"/>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128412993</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -40295,6 +42145,11 @@
       <c r="AY371" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498513</t>
         </is>
       </c>
     </row>
@@ -40398,6 +42253,11 @@
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702584</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -40499,6 +42359,11 @@
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702914</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -40598,6 +42463,11 @@
       <c r="AY374" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498514</t>
         </is>
       </c>
     </row>
@@ -40711,6 +42581,11 @@
         </is>
       </c>
       <c r="AY375" t="inlineStr"/>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409932</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -40822,6 +42697,11 @@
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128414454</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -40927,6 +42807,11 @@
         </is>
       </c>
       <c r="AY377" t="inlineStr"/>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702502</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -41031,6 +42916,11 @@
       <c r="AY378" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498519</t>
         </is>
       </c>
     </row>
@@ -41143,6 +43033,11 @@
         </is>
       </c>
       <c r="AY379" t="inlineStr"/>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409934</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -41253,6 +43148,11 @@
         </is>
       </c>
       <c r="AY380" t="inlineStr"/>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409935</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -41353,6 +43253,11 @@
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702559</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -41459,6 +43364,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498521</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -41573,6 +43483,11 @@
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410074</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -41687,6 +43602,11 @@
         </is>
       </c>
       <c r="AY384" t="inlineStr"/>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125602523</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -41787,6 +43707,11 @@
         </is>
       </c>
       <c r="AY385" t="inlineStr"/>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702534</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -41888,6 +43813,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498515</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -41987,6 +43917,11 @@
       <c r="AY387" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498511</t>
         </is>
       </c>
     </row>
@@ -42104,6 +44039,11 @@
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125602257</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -42211,6 +44151,11 @@
         </is>
       </c>
       <c r="AY389" t="inlineStr"/>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702569</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -42315,6 +44260,11 @@
       <c r="AY390" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498516</t>
         </is>
       </c>
     </row>
@@ -42419,6 +44369,11 @@
         </is>
       </c>
       <c r="AY391" t="inlineStr"/>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702554</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -42521,6 +44476,11 @@
         </is>
       </c>
       <c r="AY392" t="inlineStr"/>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702585</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -42620,6 +44580,11 @@
       <c r="AY393" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498517</t>
         </is>
       </c>
     </row>
@@ -42733,6 +44698,11 @@
         </is>
       </c>
       <c r="AY394" t="inlineStr"/>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125602258</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -42848,6 +44818,11 @@
         </is>
       </c>
       <c r="AY395" t="inlineStr"/>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128414906</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -42964,6 +44939,11 @@
         </is>
       </c>
       <c r="AY396" t="inlineStr"/>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932368</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -43076,6 +45056,11 @@
         </is>
       </c>
       <c r="AY397" t="inlineStr"/>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125931759</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -43183,6 +45168,11 @@
         </is>
       </c>
       <c r="AY398" t="inlineStr"/>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670281</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -43295,6 +45285,11 @@
         </is>
       </c>
       <c r="AY399" t="inlineStr"/>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126314579</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -43403,6 +45398,11 @@
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670368</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -43504,6 +45504,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165802</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -43604,6 +45609,11 @@
         </is>
       </c>
       <c r="AY402" t="inlineStr"/>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73849793</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -43704,6 +45714,11 @@
         </is>
       </c>
       <c r="AY403" t="inlineStr"/>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850295</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -43804,6 +45819,11 @@
         </is>
       </c>
       <c r="AY404" t="inlineStr"/>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850312</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -43917,6 +45937,11 @@
         </is>
       </c>
       <c r="AY405" t="inlineStr"/>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73849756</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -44022,6 +46047,11 @@
         </is>
       </c>
       <c r="AY406" t="inlineStr"/>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850169</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -44127,6 +46157,11 @@
         </is>
       </c>
       <c r="AY407" t="inlineStr"/>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850191</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -44241,6 +46276,11 @@
         </is>
       </c>
       <c r="AY408" t="inlineStr"/>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850223</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -44353,6 +46393,11 @@
         </is>
       </c>
       <c r="AY409" t="inlineStr"/>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850048</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -44465,6 +46510,11 @@
         </is>
       </c>
       <c r="AY410" t="inlineStr"/>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850379</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -44577,6 +46627,11 @@
         </is>
       </c>
       <c r="AY411" t="inlineStr"/>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850425</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -44689,6 +46744,11 @@
         </is>
       </c>
       <c r="AY412" t="inlineStr"/>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73849980</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -44789,6 +46849,11 @@
         </is>
       </c>
       <c r="AY413" t="inlineStr"/>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73850283</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -44890,6 +46955,11 @@
           <t>Svampinventering Ornö 2020, Länsstyrelsen Stockholm</t>
         </is>
       </c>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165788</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -44990,6 +47060,11 @@
         </is>
       </c>
       <c r="AY415" t="inlineStr"/>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702125</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -45099,6 +47174,11 @@
         </is>
       </c>
       <c r="AY416" t="inlineStr"/>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73702111</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -45207,6 +47287,11 @@
         </is>
       </c>
       <c r="AY417" t="inlineStr"/>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110700552</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -45312,6 +47397,11 @@
         </is>
       </c>
       <c r="AY418" t="inlineStr"/>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73701908</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -45412,6 +47502,11 @@
         </is>
       </c>
       <c r="AY419" t="inlineStr"/>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73701906</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -45518,6 +47613,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498525</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -45619,6 +47719,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498526</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -45736,6 +47841,11 @@
         </is>
       </c>
       <c r="AY422" t="inlineStr"/>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123423078</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -45848,6 +47958,11 @@
         </is>
       </c>
       <c r="AY423" t="inlineStr"/>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73701910</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -45954,8 +48069,438 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ424" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107498523</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ424" r:id="rId423"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -13376,7 +13376,7 @@
         <v>134942090</v>
       </c>
       <c r="B115" t="n">
-        <v>99173</v>
+        <v>99220</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>134944166</v>
       </c>
       <c r="B171" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>134944032</v>
       </c>
       <c r="B173" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>134944605</v>
       </c>
       <c r="B241" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -13608,7 +13608,7 @@
         <v>136011680</v>
       </c>
       <c r="B117" t="n">
-        <v>99255</v>
+        <v>99272</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>136011820</v>
       </c>
       <c r="B180" t="n">
-        <v>106325</v>
+        <v>106345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -13608,7 +13608,7 @@
         <v>136011680</v>
       </c>
       <c r="B117" t="n">
-        <v>99272</v>
+        <v>99273</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>136011820</v>
       </c>
       <c r="B180" t="n">
-        <v>106345</v>
+        <v>106347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -13608,7 +13608,7 @@
         <v>136011680</v>
       </c>
       <c r="B117" t="n">
-        <v>99273</v>
+        <v>99274</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>136011820</v>
       </c>
       <c r="B180" t="n">
-        <v>106347</v>
+        <v>106348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -13608,7 +13608,7 @@
         <v>136011680</v>
       </c>
       <c r="B117" t="n">
-        <v>99274</v>
+        <v>99275</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>136011820</v>
       </c>
       <c r="B180" t="n">
-        <v>106348</v>
+        <v>106349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -13608,7 +13608,7 @@
         <v>136011680</v>
       </c>
       <c r="B117" t="n">
-        <v>99275</v>
+        <v>99281</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>136011820</v>
       </c>
       <c r="B180" t="n">
-        <v>106349</v>
+        <v>106355</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -13608,7 +13608,7 @@
         <v>136011680</v>
       </c>
       <c r="B117" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>136011820</v>
       </c>
       <c r="B180" t="n">
-        <v>106355</v>
+        <v>106356</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -13608,7 +13608,7 @@
         <v>136011680</v>
       </c>
       <c r="B117" t="n">
-        <v>99282</v>
+        <v>99293</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>136011820</v>
       </c>
       <c r="B180" t="n">
-        <v>106356</v>
+        <v>106367</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/Norra skogen artfynd.xlsx
+++ b/artfynd/Norra skogen artfynd.xlsx
@@ -13608,7 +13608,7 @@
         <v>136011680</v>
       </c>
       <c r="B117" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>136011820</v>
       </c>
       <c r="B180" t="n">
-        <v>106367</v>
+        <v>106380</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
